--- a/docs/package/05_Delivery/Upload_Templates/Bank_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Bank_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="81">
   <si>
     <t xml:space="preserve">Bank Code</t>
   </si>
@@ -24,7 +24,7 @@
     <t xml:space="preserve">Bank Branch</t>
   </si>
   <si>
-    <t xml:space="preserve">IFSC / SWIFT Code</t>
+    <t xml:space="preserve">SWIFT Code</t>
   </si>
   <si>
     <t xml:space="preserve">Address Line 1</t>
@@ -36,114 +36,117 @@
     <t xml:space="preserve">Address Line 3</t>
   </si>
   <si>
+    <t xml:space="preserve">City / Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CITI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citibank, N.A. (Philippine Branch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonifacio Global City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CITIPHMX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Bonifacio High Street, 5th Ave.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taguig City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metro Manila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philippines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+63 2 8995 9999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customer.service@citi.example.ph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowed values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other accepted headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bankCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bankName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bankBranch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWIFT / BIC code of the branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifscCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AddressLine1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AddressLine2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AddressLine3</t>
+  </si>
+  <si>
     <t xml:space="preserve">City</t>
   </si>
   <si>
-    <t xml:space="preserve">State</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Union Bank of the Philippines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ortigas Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBPHPHMM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UnionBank Plaza, Meralco Ave.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pasig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metro Manila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philippines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+63 2 8841 8600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">customer.service@unionbank.example.ph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universal Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allowed values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other accepted headers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bankCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bankName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bankBranch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SWIFT / BIC code of the branch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifscCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddressLine1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddressLine2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddressLine3</t>
-  </si>
-  <si>
     <t xml:space="preserve">state</t>
   </si>
   <si>
@@ -213,7 +216,7 @@
     <t xml:space="preserve">Required columns</t>
   </si>
   <si>
-    <t xml:space="preserve">Bank Code, Bank Name, Bank Branch, IFSC / SWIFT Code, City, State, Country, Phone, Email ID (dark red headers on the Data sheet). Other columns may be left empty or removed.</t>
+    <t xml:space="preserve">Bank Code, Bank Name, Bank Branch, SWIFT Code, City / Municipality, Province, Country, Phone, Email ID (dark red headers on the Data sheet). Other columns may be left empty or removed.</t>
   </si>
   <si>
     <t xml:space="preserve">Header row</t>
@@ -244,6 +247,9 @@
   </si>
   <si>
     <t xml:space="preserve">Each row creates a new record, checked exactly like Add on the screen. A row whose code already exists is refused (edit existing records on the screen).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The main Philippine banks are shipped (BDO, BPI, Metrobank, Land Bank, PNB, Security Bank, UnionBank, RCBC, China Bank, EastWest, DBP, PSBank, AUB, Maybank, PBCom, Bank of Commerce, Veterans Bank) with their SWIFT codes. Add the others you deal with.</t>
   </si>
   <si>
     <t xml:space="preserve">Source</t>
@@ -384,11 +390,11 @@
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
@@ -644,6 +650,9 @@
       <c r="E9" s="0" t="s">
         <v>20</v>
       </c>
+      <c r="F9" s="4" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
@@ -659,7 +668,7 @@
         <v>21</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -690,7 +699,7 @@
         <v>23</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -712,13 +721,13 @@
         <v>32</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>24</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -729,16 +738,16 @@
         <v>39</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -749,13 +758,13 @@
         <v>39</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -765,7 +774,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -774,106 +783,111 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="s">
-        <v>77</v>
-      </c>
       <c r="B13" s="4" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Bank_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Bank_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="81">
   <si>
     <t xml:space="preserve">Bank Code</t>
   </si>
@@ -21,6 +21,9 @@
     <t xml:space="preserve">Bank Name</t>
   </si>
   <si>
+    <t xml:space="preserve">Short Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bank Branch</t>
   </si>
   <si>
@@ -123,6 +126,12 @@
     <t xml:space="preserve">bankName</t>
   </si>
   <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shortName</t>
+  </si>
+  <si>
     <t xml:space="preserve">bankBranch</t>
   </si>
   <si>
@@ -132,9 +141,6 @@
     <t xml:space="preserve">ifscCode</t>
   </si>
   <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
     <t xml:space="preserve">AddressLine1</t>
   </si>
   <si>
@@ -195,12 +201,6 @@
     <t xml:space="preserve">Master &gt; Finance &gt; Bank &gt; Upload</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/masters/bank/upload (multipart field "file")</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -231,10 +231,10 @@
     <t xml:space="preserve">The rows under the header on the Data sheet are samples. Delete them before you upload your own data.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dates and amounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter dates as YYYY-MM-DD and amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
+    <t xml:space="preserve">Amounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
   </si>
   <si>
     <t xml:space="preserve">What happens on errors</t>
@@ -252,10 +252,10 @@
     <t xml:space="preserve">The main Philippine banks are shipped (BDO, BPI, Metrobank, Land Bank, PNB, Security Bank, UnionBank, RCBC, China Bank, EastWest, DBP, PSBank, AUB, Maybank, PBCom, Bank of Commerce, Veterans Bank) with their SWIFT codes. Add the others you deal with.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -263,9 +263,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -292,8 +292,42 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F6B76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,6 +355,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -352,9 +404,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -375,6 +427,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,40 +443,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20" customHeight="1">
+    <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -426,7 +486,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="7" t="s">
@@ -438,27 +498,27 @@
       <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="0" t="s">
         <v>17</v>
       </c>
       <c r="D2" s="0" t="s">
@@ -467,7 +527,7 @@
       <c r="E2" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="F2" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I2" s="0" t="s">
@@ -479,11 +539,14 @@
       <c r="K2" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="L2" s="0" t="s">
         <v>24</v>
       </c>
       <c r="N2" s="0" t="s">
         <v>25</v>
+      </c>
+      <c r="O2" s="0" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -493,7 +556,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -506,22 +569,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -529,16 +592,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -546,16 +609,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -563,16 +626,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -580,16 +640,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -597,16 +657,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -614,13 +674,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>20</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -628,13 +691,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -642,16 +705,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -659,16 +719,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -676,13 +736,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>22</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +753,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>23</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -707,10 +767,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -718,16 +784,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -735,19 +795,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="E15" s="0" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -755,16 +812,36 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="4" t="s">
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>53</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +851,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -783,110 +860,102 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="s">
-        <v>76</v>
-      </c>
       <c r="B12" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>79</v>
+      </c>
       <c r="B13" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="4" t="s">
         <v>80</v>
       </c>
     </row>
